--- a/毕业论文/output.xlsx
+++ b/毕业论文/output.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimes\PycharmProjects\pythonProject\毕业论文\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jimes\PycharmProjects\pythonProject\毕业论文\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF306FB1-1176-439B-A314-672AC46513D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA72DAA1-7015-4BD8-A563-C55630315280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,22 +19,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="213">
   <si>
     <t>县</t>
   </si>
@@ -339,9 +328,6 @@
     <t>33.207475,107.171209</t>
   </si>
   <si>
-    <t>33.23081,107.169867</t>
-  </si>
-  <si>
     <t>33.191321,107.379943</t>
   </si>
   <si>
@@ -379,9 +365,6 @@
   </si>
   <si>
     <t>33.170244,106.753032</t>
-  </si>
-  <si>
-    <t>33.165689,106.890524</t>
   </si>
   <si>
     <t>33.145204,106.846568</t>
@@ -684,15 +667,35 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>坐标啊</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>缺货</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>类别</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>坐标点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>城关镇</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>总缺货</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>33.23081,107.169867</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>33.165689,106.890524</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>32.465878,107.483882</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -877,7 +880,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -911,9 +914,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1248,42 +1248,45 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>209</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="L1" s="23" t="s">
-        <v>209</v>
+        <v>201</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>206</v>
       </c>
       <c r="M1" s="22" t="s">
         <v>207</v>
       </c>
       <c r="N1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D2">
         <v>8.2799999999999994</v>
@@ -1307,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N2">
         <v>8.2799999999999994</v>
@@ -1317,7 +1320,7 @@
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="13" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="15" t="s">
@@ -1360,7 +1363,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="B4" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -1396,7 +1399,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="B5" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="15" t="s">
@@ -1432,7 +1435,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
+      <c r="B6" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
@@ -1469,7 +1472,7 @@
     </row>
     <row r="7" spans="1:15" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17"/>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="19" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="17" t="s">
@@ -1500,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N7">
         <v>0.23</v>
@@ -1546,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N8">
         <v>0.24</v>
@@ -1582,7 +1585,7 @@
         <v>2</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N9">
         <v>0.26</v>
@@ -1618,7 +1621,7 @@
         <v>2</v>
       </c>
       <c r="M10" s="21" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N10" s="17">
         <v>0.23</v>
@@ -1626,11 +1629,11 @@
     </row>
     <row r="11" spans="1:15" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17"/>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="19" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>101</v>
+        <v>210</v>
       </c>
       <c r="D11" s="17">
         <v>1.87</v>
@@ -1657,7 +1660,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N11">
         <v>2.75</v>
@@ -1667,11 +1670,11 @@
       <c r="A12" t="s">
         <v>7</v>
       </c>
-      <c r="B12" t="s">
-        <v>200</v>
+      <c r="B12" s="13" t="s">
+        <v>198</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12">
         <v>1.3</v>
@@ -1703,7 +1706,7 @@
         <v>2</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N12" s="12">
         <v>0.4</v>
@@ -1714,7 +1717,7 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13">
         <v>3.48</v>
@@ -1739,13 +1742,13 @@
         <v>3</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N13" s="12">
         <v>0.72</v>
       </c>
       <c r="O13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1753,7 +1756,7 @@
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14" s="11">
         <v>1.46</v>
@@ -1778,7 +1781,7 @@
         <v>3</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N14" s="12">
         <v>0.97</v>
@@ -1789,7 +1792,7 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D15" s="11">
         <v>1.89</v>
@@ -1814,7 +1817,7 @@
         <v>3</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N15" s="12">
         <v>0.69</v>
@@ -1825,7 +1828,7 @@
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D16">
         <v>0.7</v>
@@ -1850,7 +1853,7 @@
         <v>3</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N16" s="12">
         <v>0.27</v>
@@ -1861,7 +1864,7 @@
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D17">
         <v>0.81</v>
@@ -1886,7 +1889,7 @@
         <v>3</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N17" s="12">
         <v>1.01</v>
@@ -1897,7 +1900,7 @@
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D18" s="11">
         <v>1.03</v>
@@ -1922,7 +1925,7 @@
         <v>3</v>
       </c>
       <c r="M18" s="20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N18" s="18">
         <v>0.21</v>
@@ -1933,7 +1936,7 @@
         <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D19">
         <v>2.15</v>
@@ -1958,7 +1961,7 @@
         <v>4</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N19" s="12">
         <v>0.97</v>
@@ -1969,7 +1972,7 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" s="11">
         <v>0.62</v>
@@ -1994,7 +1997,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N20" s="12">
         <v>0.43</v>
@@ -2006,7 +2009,7 @@
         <v>33</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D21" s="18">
         <v>0.46</v>
@@ -2033,13 +2036,13 @@
         <v>2</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N21" s="12">
         <v>0.3</v>
       </c>
       <c r="O21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
@@ -2050,7 +2053,7 @@
         <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D22">
         <v>0.34</v>
@@ -2081,7 +2084,7 @@
         <v>6</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N22" s="12">
         <v>0.36</v>
@@ -2091,11 +2094,11 @@
       <c r="A23" t="s">
         <v>9</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D23" s="11">
         <v>9.68</v>
@@ -2127,7 +2130,7 @@
         <v>7</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N23" s="12">
         <v>1.21</v>
@@ -2138,7 +2141,7 @@
         <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D24">
         <v>1.21</v>
@@ -2163,18 +2166,18 @@
         <v>1</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N24" s="12">
         <v>0.66</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
+      <c r="B25" s="13" t="s">
         <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>211</v>
       </c>
       <c r="D25">
         <v>2.71</v>
@@ -2199,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="N25" s="18">
         <v>0.45</v>
@@ -2210,7 +2213,7 @@
         <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D26">
         <v>1.34</v>
@@ -2240,7 +2243,7 @@
         <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D27" s="13">
         <v>1.95</v>
@@ -2270,7 +2273,7 @@
         <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D28">
         <v>0.36</v>
@@ -2296,11 +2299,11 @@
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
+      <c r="B29" s="13" t="s">
         <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D29">
         <v>0.89</v>
@@ -2330,7 +2333,7 @@
         <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D30" s="13">
         <v>3.94</v>
@@ -2360,7 +2363,7 @@
         <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D31">
         <v>1.61</v>
@@ -2390,7 +2393,7 @@
         <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D32" s="13">
         <v>1.01</v>
@@ -2420,7 +2423,7 @@
         <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D33">
         <v>0.53</v>
@@ -2451,7 +2454,7 @@
         <v>46</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D34" s="19">
         <v>1.86</v>
@@ -2486,7 +2489,7 @@
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D35">
         <v>0.63</v>
@@ -2523,7 +2526,7 @@
         <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D36">
         <v>0.36</v>
@@ -2553,7 +2556,7 @@
         <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D37">
         <v>1.88</v>
@@ -2583,7 +2586,7 @@
         <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D38">
         <v>1.06</v>
@@ -2613,7 +2616,7 @@
         <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D39">
         <v>1.1299999999999999</v>
@@ -2643,7 +2646,7 @@
         <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D40">
         <v>3.1</v>
@@ -2674,7 +2677,7 @@
         <v>53</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D41" s="17">
         <v>0.46</v>
@@ -2710,7 +2713,7 @@
         <v>54</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D42" s="12">
         <v>6.75</v>
@@ -2747,7 +2750,7 @@
         <v>55</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D43">
         <v>0.4</v>
@@ -2773,11 +2776,11 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
+      <c r="B44" s="13" t="s">
         <v>56</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D44" s="13">
         <v>0.72</v>
@@ -2807,7 +2810,7 @@
         <v>57</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D45">
         <v>0.97</v>
@@ -2837,7 +2840,7 @@
         <v>58</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D46" s="13">
         <v>0.69</v>
@@ -2867,7 +2870,7 @@
         <v>59</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D47">
         <v>0.27</v>
@@ -2897,7 +2900,7 @@
         <v>60</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D48" s="13">
         <v>1.01</v>
@@ -2928,7 +2931,7 @@
         <v>61</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D49" s="17">
         <v>0.21</v>
@@ -2960,10 +2963,10 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C50" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D50" s="11">
         <v>0.6</v>
@@ -3000,7 +3003,7 @@
         <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D51" s="11">
         <v>0.93</v>
@@ -3030,7 +3033,7 @@
         <v>63</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D52" s="14">
         <v>0.97</v>
@@ -3056,11 +3059,11 @@
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
+      <c r="B53" s="13" t="s">
         <v>64</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="D53" s="14">
         <v>0.43</v>
@@ -3090,7 +3093,7 @@
         <v>65</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D54">
         <v>0.39</v>
@@ -3120,7 +3123,7 @@
         <v>66</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D55" s="14">
         <v>0.36</v>
@@ -3150,7 +3153,7 @@
         <v>67</v>
       </c>
       <c r="C56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D56" s="11">
         <v>0.49</v>
@@ -3180,7 +3183,7 @@
         <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D57">
         <v>1.18</v>
@@ -3210,7 +3213,7 @@
         <v>69</v>
       </c>
       <c r="C58" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D58">
         <v>1.39</v>
@@ -3240,7 +3243,7 @@
         <v>70</v>
       </c>
       <c r="C59" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D59">
         <v>0.8</v>
@@ -3270,7 +3273,7 @@
         <v>47</v>
       </c>
       <c r="C60" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D60" s="11">
         <v>0.67</v>
@@ -3296,11 +3299,11 @@
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
+      <c r="B61" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D61" s="14">
         <v>1.21</v>
@@ -3330,7 +3333,7 @@
         <v>72</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D62">
         <v>0.66</v>
@@ -3360,7 +3363,7 @@
         <v>73</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D63" s="14">
         <v>0.45</v>
@@ -3390,7 +3393,7 @@
         <v>74</v>
       </c>
       <c r="C64" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D64" s="11">
         <v>5.09</v>
@@ -3420,7 +3423,7 @@
         <v>75</v>
       </c>
       <c r="C65" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D65">
         <v>1.1399999999999999</v>
@@ -3450,7 +3453,7 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D66">
         <v>1.33</v>
@@ -3480,7 +3483,7 @@
         <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D67" s="11">
         <v>1.1000000000000001</v>
@@ -3510,7 +3513,7 @@
         <v>78</v>
       </c>
       <c r="C68" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D68">
         <v>0.83</v>
@@ -3541,7 +3544,7 @@
         <v>79</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D69" s="21">
         <v>1.06</v>
@@ -3573,10 +3576,10 @@
         <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>54</v>
+        <v>208</v>
       </c>
       <c r="C70" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D70">
         <v>1.1200000000000001</v>
@@ -3613,7 +3616,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D71">
         <v>0.37</v>
@@ -3643,7 +3646,7 @@
         <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D72">
         <v>0.35</v>
@@ -3673,7 +3676,7 @@
         <v>82</v>
       </c>
       <c r="C73" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D73">
         <v>0.34</v>
@@ -3703,7 +3706,7 @@
         <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D74">
         <v>0.76</v>
@@ -3733,7 +3736,7 @@
         <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D75">
         <v>0.11</v>
@@ -3763,7 +3766,7 @@
         <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D76">
         <v>0.25</v>
@@ -3794,7 +3797,7 @@
         <v>86</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D77" s="17">
         <v>0.21</v>
@@ -3829,7 +3832,7 @@
         <v>87</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D78">
         <v>0.23</v>
@@ -3866,7 +3869,7 @@
         <v>88</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D79">
         <v>0.24</v>
@@ -3892,7 +3895,7 @@
         <v>89</v>
       </c>
       <c r="C80" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D80">
         <v>0.11</v>
@@ -3918,7 +3921,7 @@
         <v>90</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D81">
         <v>0.26</v>
@@ -3944,7 +3947,7 @@
         <v>91</v>
       </c>
       <c r="C82" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D82">
         <v>0.45</v>
@@ -3967,10 +3970,10 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D83">
         <v>0.28000000000000003</v>
@@ -3985,10 +3988,10 @@
         <v>82</v>
       </c>
       <c r="H83" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J83" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K83">
         <v>0.23</v>
@@ -4003,7 +4006,7 @@
         <v>92</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D84" s="17">
         <v>1.0900000000000001</v>
@@ -4029,10 +4032,10 @@
     </row>
     <row r="85" spans="1:13" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -4047,7 +4050,7 @@
         <v>107.07853900000001</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K85" s="9">
         <f>SUM(K2:K84)</f>
@@ -4057,7 +4060,7 @@
     </row>
     <row r="86" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
       <c r="B86" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -4081,7 +4084,7 @@
     </row>
     <row r="87" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
       <c r="B87" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -4106,7 +4109,7 @@
     </row>
     <row r="88" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
       <c r="B88" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C88">
         <v>3</v>
@@ -4130,7 +4133,7 @@
     </row>
     <row r="89" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
       <c r="B89" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C89">
         <v>4</v>
@@ -4154,7 +4157,7 @@
     </row>
     <row r="90" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
       <c r="B90" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C90">
         <v>5</v>
@@ -4178,7 +4181,7 @@
     </row>
     <row r="91" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
       <c r="B91" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C91">
         <v>6</v>
@@ -4202,7 +4205,7 @@
     </row>
     <row r="92" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="B92" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C92">
         <v>7</v>
@@ -4227,7 +4230,7 @@
     </row>
     <row r="93" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
       <c r="B93" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C93">
         <v>8</v>
@@ -4254,7 +4257,7 @@
     </row>
     <row r="94" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
       <c r="B94" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C94">
         <v>9</v>
@@ -4279,7 +4282,7 @@
     </row>
     <row r="95" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
       <c r="B95" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C95">
         <v>10</v>
@@ -4313,27 +4316,26 @@
     </row>
     <row r="97" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G97" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="98" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G98" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H98" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="99" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G99" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H99" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/毕业论文/output.xlsx
+++ b/毕业论文/output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jimes\PycharmProjects\pythonProject\毕业论文\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA72DAA1-7015-4BD8-A563-C55630315280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C104F6-2E89-47E2-A856-2EE0BD085431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
